--- a/Wusong/旧通信协议（用于武松）4-15.xlsx
+++ b/Wusong/旧通信协议（用于武松）4-15.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\单片机项目\Source\Project\Wusong_New_1.7_fixed\Wusong\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="29865" windowHeight="13455" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="武松新协议" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="154">
   <si>
     <t>安卓串口通信协议</t>
   </si>
@@ -360,6 +366,256 @@
   </si>
   <si>
     <t>0xFF</t>
+  </si>
+  <si>
+    <t>重传ID号</t>
+  </si>
+  <si>
+    <t>唯一ID号</t>
+  </si>
+  <si>
+    <t>功能码1</t>
+  </si>
+  <si>
+    <t>功能码2</t>
+  </si>
+  <si>
+    <t>数据位3</t>
+  </si>
+  <si>
+    <t>数据位4</t>
+  </si>
+  <si>
+    <t>应答位</t>
+  </si>
+  <si>
+    <t>补充位</t>
+  </si>
+  <si>
+    <t>CRC16校验位1</t>
+  </si>
+  <si>
+    <t>CRC16校验位2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>0xF7</t>
+  </si>
+  <si>
+    <t>0xF0</t>
+  </si>
+  <si>
+    <t>球盘→安卓</t>
+  </si>
+  <si>
+    <t>ID号</t>
+  </si>
+  <si>
+    <t>补充位2</t>
+  </si>
+  <si>
+    <t>投币1币</t>
+  </si>
+  <si>
+    <t>编号(0x01-0x05)</t>
+  </si>
+  <si>
+    <t>0x01(短按)0x02(长按)0x03(松开)</t>
+  </si>
+  <si>
+    <t>编号(0x01-0x03)</t>
+  </si>
+  <si>
+    <t>4字节数据（剩余未吐出数量）</t>
+  </si>
+  <si>
+    <t>剩余物品数</t>
+  </si>
+  <si>
+    <t>4字节数据(剩余数量)</t>
+  </si>
+  <si>
+    <t>0x00（珠子）0x01（卡片）</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>编号(0x00-0x11)</t>
+  </si>
+  <si>
+    <t>安卓→球盘</t>
+  </si>
+  <si>
+    <t>4字节数据（吐出珠子数量）</t>
+  </si>
+  <si>
+    <t>0x00(瓷珠)0x01（钢珠）</t>
+  </si>
+  <si>
+    <t>吐卡、吐票</t>
+  </si>
+  <si>
+    <t>4字节数据（吐出卡片数量）</t>
+  </si>
+  <si>
+    <t>亮度等级(0x00-0x0A)</t>
+  </si>
+  <si>
+    <t>场景编号(0x00-0xFF)</t>
+  </si>
+  <si>
+    <t>0x00(无模式)0x01(弹珠机模式)0x02(小游戏模式)</t>
+  </si>
+  <si>
+    <t>16字节数据</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哪一盏灯亮起就将该字节位置1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将16位数据拆成2个字节发送</t>
+    </r>
+  </si>
+  <si>
+    <t>吐出剩余物品</t>
+  </si>
+  <si>
+    <t>洞内电磁阀推出</t>
+  </si>
+  <si>
+    <t>灯组流动</t>
+  </si>
+  <si>
+    <t>0x21</t>
+  </si>
+  <si>
+    <t>灯数（0x01-0x03）</t>
+  </si>
+  <si>
+    <t>停留时长（0x00-0x03）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x00：100ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x01:200ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x02:300ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0x03:400ms</t>
+    </r>
+  </si>
+  <si>
+    <t>球盘重启</t>
   </si>
 </sst>
 </file>
@@ -372,7 +628,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,6 +657,39 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +706,18 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -564,7 +865,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,7 +874,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -591,13 +892,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA9D08E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF700FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,12 +1113,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -808,6 +1148,43 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -929,139 +1306,250 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1072,44 +1560,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1203,6 +1688,53 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13536295" y="7981315"/>
+          <a:ext cx="6134100" cy="4391660"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>226695</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>188595</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>151130</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17627600" y="5855970"/>
           <a:ext cx="6134100" cy="4391660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1472,1146 +2004,1146 @@
   <dimension ref="A1:I50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.1083333333333" style="1" customWidth="1"/>
-    <col min="2" max="3" width="15.3833333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.6333333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.15" style="2" customWidth="1"/>
-    <col min="6" max="8" width="15.3833333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="32.8833333333333" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="17.1083333333333" style="38" customWidth="1"/>
+    <col min="2" max="3" width="15.3833333333333" style="39" customWidth="1"/>
+    <col min="4" max="4" width="21.6333333333333" style="39" customWidth="1"/>
+    <col min="5" max="5" width="26.15" style="39" customWidth="1"/>
+    <col min="6" max="8" width="15.3833333333333" style="39" customWidth="1"/>
+    <col min="9" max="9" width="32.8833333333333" style="39" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="43" customHeight="1" spans="1:9">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="42" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="B3" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="47" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:9">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="51" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="14"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="51"/>
     </row>
     <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="14" t="s">
+      <c r="D8" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="14"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="51"/>
     </row>
     <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="14"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="51"/>
     </row>
     <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="14"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="51"/>
     </row>
     <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="B11" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="14" t="s">
+      <c r="D11" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="14"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="51"/>
     </row>
     <row r="12" customHeight="1" spans="1:9">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="D12" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="14"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="51"/>
     </row>
     <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="14" t="s">
+      <c r="D13" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="14"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="51"/>
     </row>
     <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="D14" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="14"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="51"/>
     </row>
     <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="14" t="s">
+      <c r="D15" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="14"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="51"/>
     </row>
     <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="D16" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="14"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="51"/>
     </row>
     <row r="17" customHeight="1" spans="1:9">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="14" t="s">
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="51" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="14" t="s">
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="51" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="B19" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="15" t="s">
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="52" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="52" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="52" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="14" t="s">
+      <c r="B22" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="14"/>
+      <c r="E22" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="51"/>
     </row>
     <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="15" t="s">
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="52" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="15" t="s">
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="52" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="15"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="52"/>
     </row>
     <row r="26" customHeight="1" spans="1:9">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="14" t="s">
+      <c r="B26" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="14"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="51"/>
     </row>
     <row r="27" customHeight="1" spans="1:9">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="14" t="s">
+      <c r="B27" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="14"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="51"/>
     </row>
     <row r="28" customHeight="1" spans="1:9">
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
     </row>
     <row r="29" customHeight="1" spans="1:9">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
     </row>
     <row r="30" customHeight="1" spans="1:9">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I30" s="51" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="14" t="s">
+      <c r="B31" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="14"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="51"/>
     </row>
     <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="14" t="s">
+      <c r="B32" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="14"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="51"/>
     </row>
     <row r="33" customHeight="1" spans="1:9">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="14" t="s">
+      <c r="B33" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="14" t="s">
+      <c r="D33" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="14"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="51"/>
     </row>
     <row r="34" customHeight="1" spans="1:9">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="14" t="s">
+      <c r="B34" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="14" t="s">
+      <c r="D34" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="14"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="51"/>
     </row>
     <row r="35" customHeight="1" spans="1:9">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="14" t="s">
+      <c r="B35" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="14"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" customHeight="1" spans="1:9">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="14" t="s">
+      <c r="B36" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="14"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" customHeight="1" spans="1:9">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="B37" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="14" t="s">
+      <c r="D37" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="15" t="s">
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="52" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="38" ht="41" customHeight="1" spans="1:9">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="14" t="s">
+      <c r="B38" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="16" t="s">
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="34" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:9">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="14" t="s">
+      <c r="D39" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="15" t="s">
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="52" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:9">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="14" t="s">
+      <c r="B40" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="14" t="s">
+      <c r="D40" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="16" t="s">
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="34" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:9">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="14" t="s">
+      <c r="B41" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="14"/>
+      <c r="D41" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="51"/>
     </row>
     <row r="42" customHeight="1" spans="1:9">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="14" t="s">
+      <c r="B42" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="14"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="51"/>
     </row>
     <row r="43" customHeight="1" spans="1:9">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="14"/>
+      <c r="D43" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="51"/>
     </row>
     <row r="44" customHeight="1" spans="1:9">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="14" t="s">
+      <c r="B44" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D44" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="14"/>
+      <c r="D44" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="51"/>
     </row>
     <row r="45" customHeight="1" spans="1:9">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="14" t="s">
+      <c r="B45" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="14"/>
+      <c r="D45" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="51"/>
     </row>
     <row r="46" customHeight="1" spans="1:9">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="14" t="s">
+      <c r="B46" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="14"/>
+      <c r="D46" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="51"/>
     </row>
     <row r="47" customHeight="1" spans="1:9">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="14" t="s">
+      <c r="B47" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="14"/>
+      <c r="D47" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="51"/>
     </row>
     <row r="48" customHeight="1" spans="1:9">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="14" t="s">
+      <c r="B48" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="D48" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E48" s="14" t="s">
+      <c r="D48" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="E48" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" s="14"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="51"/>
     </row>
     <row r="49" customHeight="1" spans="1:9">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="14" t="s">
+      <c r="B49" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E49" s="14" t="s">
+      <c r="D49" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I49" s="14"/>
+      <c r="F49" s="51"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="51"/>
     </row>
     <row r="50" customHeight="1" spans="1:9">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="14" t="s">
+      <c r="B50" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="14" t="s">
+      <c r="D50" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" s="14"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2631,12 +3163,1697 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:Q45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="17.1083333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.56666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.8" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.5416666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.58333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.3" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.8416666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="30.1083333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9" style="2"/>
+    <col min="12" max="12" width="27.825" style="2" customWidth="1"/>
+    <col min="13" max="15" width="9" style="2"/>
+    <col min="16" max="16" width="17.8833333333333" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" customHeight="1" spans="1:15">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" ht="27" spans="1:15">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" ht="20.25" spans="1:15">
+      <c r="A5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+    </row>
+    <row r="6" ht="27" spans="1:15">
+      <c r="A6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:15">
+      <c r="A9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="27" spans="1:15">
+      <c r="A10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" ht="27" spans="1:15">
+      <c r="A22" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" ht="20.25" spans="1:15">
+      <c r="A24" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="K25" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="L25" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="M25" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="N25" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="O25" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" ht="27" spans="1:15">
+      <c r="A32" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" ht="66" spans="1:17">
+      <c r="A33" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="J33" s="30"/>
+      <c r="K33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P33" s="31" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" ht="33" spans="1:17">
+      <c r="A34" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="K34" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P34" s="34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J42" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" ht="54" spans="1:17">
+      <c r="A43" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="J43" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q43" s="37"/>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P45" s="37"/>
+      <c r="Q45" s="37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:O5"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B24:O24"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="I33:J33"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2650,4 +4867,16 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
 </file>